--- a/mst-qms/원본_정정본/2_프로세스_절차서_지침_양식/4_양식/(관리자)자격인정평가표.xlsx
+++ b/mst-qms/원본_정정본/2_프로세스_절차서_지침_양식/4_양식/(관리자)자격인정평가표.xlsx
@@ -1445,7 +1445,7 @@
         <color theme="1"/>
         <sz val="16.0"/>
       </rPr>
-      <t>일          대표이사   김 맹 권</t>
+      <t>일          대표이사   김 명 권</t>
     </r>
   </si>
 </sst>
